--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1211,7 +1211,7 @@
         <v>4.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>2.5</v>
@@ -1220,7 +1220,7 @@
         <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U5" t="n">
         <v>2.19</v>
@@ -1232,7 +1232,7 @@
         <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.1</v>
@@ -1244,10 +1244,10 @@
         <v>1.49</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD5" t="n">
         <v>1.63</v>
@@ -1256,7 +1256,7 @@
         <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG5" t="n">
         <v>2.5</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="O3" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
         <v>3.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="P6" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="S6" t="n">
         <v>1.43</v>
@@ -1415,10 +1415,10 @@
         <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.52</v>
+        <v>5.1</v>
       </c>
       <c r="R4" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.36</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z4" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="P6" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="R6" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>3.08</v>
+        <v>3.33</v>
       </c>
       <c r="V6" t="n">
         <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
         <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -1052,49 +1052,49 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.06</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
         <v>1.98</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.39</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z3" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.32</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.39</v>
-      </c>
       <c r="Z4" t="n">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>1.91</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1367,10 +1367,10 @@
         <v>3.15</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
         <v>2.06</v>
@@ -1382,16 +1382,16 @@
         <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>3.33</v>
+        <v>3.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
         <v>1.36</v>
@@ -1403,13 +1403,13 @@
         <v>2.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.02</v>
@@ -1418,7 +1418,7 @@
         <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>1.95</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>5.1</v>
       </c>
       <c r="R4" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.9</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.22</v>
-      </c>
       <c r="AA4" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.91</v>
+        <v>1.09</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1364,16 +1364,16 @@
         <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="R6" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="S6" t="n">
         <v>1.45</v>
@@ -1382,7 +1382,7 @@
         <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V6" t="n">
         <v>1.29</v>
@@ -1391,7 +1391,7 @@
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
         <v>1.36</v>
@@ -1403,13 +1403,13 @@
         <v>2.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
         <v>1.02</v>
@@ -1434,7 +1434,7 @@
         <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.66</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.95</v>
+        <v>1.09</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
         <v>2.93</v>
@@ -1400,16 +1400,16 @@
         <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AB6" t="n">
         <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.96</v>
+        <v>4.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
         <v>1.02</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
         <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="Q3" t="n">
         <v>2.25</v>
@@ -899,49 +899,49 @@
         <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
         <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
         <v>3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
         <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>1.49</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
         <v>2.16</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
         <v>3.04</v>
@@ -1376,13 +1376,13 @@
         <v>1.94</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
         <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V6" t="n">
         <v>1.29</v>
@@ -1400,10 +1400,10 @@
         <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>4.12</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>5.03</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.36</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AD3" t="n">
         <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.82</v>
+        <v>1.06</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.03</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK4" t="n">
         <v>2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.06</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1367,19 +1367,19 @@
         <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
         <v>2.93</v>
       </c>
       <c r="R6" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="S6" t="n">
         <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
         <v>3.12</v>
@@ -1403,13 +1403,13 @@
         <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.12</v>
+        <v>3.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
         <v>1.02</v>
@@ -1418,7 +1418,7 @@
         <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.03</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK3" t="n">
         <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.06</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
         <v>2.5</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -887,7 +887,7 @@
         <v>1.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
         <v>4.16</v>
@@ -896,7 +896,7 @@
         <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
         <v>1.33</v>
@@ -905,7 +905,7 @@
         <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.37</v>
@@ -914,35 +914,35 @@
         <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
         <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="R6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
         <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
         <v>3.12</v>
@@ -1394,7 +1394,7 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
         <v>2.7</v>
@@ -1403,10 +1403,10 @@
         <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.96</v>
+        <v>4.33</v>
       </c>
       <c r="AD6" t="n">
         <v>1.17</v>
@@ -1415,10 +1415,10 @@
         <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>4.16</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.91</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.75</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
         <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.5</v>
+        <v>3.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1241,10 +1241,10 @@
         <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AC5" t="n">
         <v>2.16</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>4.16</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.91</v>
       </c>
-      <c r="U3" t="n">
-        <v>2.75</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.5</v>
+        <v>3.93</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>2.34</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="U4" t="n">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
         <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1364,61 +1364,61 @@
         <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>3.35</v>
@@ -899,16 +899,16 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.06</v>
@@ -920,25 +920,25 @@
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB3" t="n">
         <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.93</v>
+        <v>4.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
         <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AG3" t="n">
         <v>1.75</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.63</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U3" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
         <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.63</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>4.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.84</v>
+        <v>1.13</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="O2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T2" t="n">
         <v>3.75</v>
       </c>
-      <c r="P2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="U2" t="n">
         <v>2.2</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.18</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA2" t="n">
         <v>1.47</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.63</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>4.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>1.13</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.87</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>2.34</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U4" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.07</v>
+        <v>3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="O5" t="n">
         <v>3.9</v>
@@ -1211,16 +1211,16 @@
         <v>4.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
         <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
         <v>2.19</v>
@@ -1229,16 +1229,16 @@
         <v>1.65</v>
       </c>
       <c r="W5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.12</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA5" t="n">
         <v>1.49</v>
@@ -1247,7 +1247,7 @@
         <v>2.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
         <v>1.63</v>
@@ -1256,7 +1256,7 @@
         <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
         <v>2.5</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -728,7 +728,7 @@
         <v>1.88</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P2" t="n">
         <v>3.2</v>
@@ -737,7 +737,7 @@
         <v>2.42</v>
       </c>
       <c r="R2" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S2" t="n">
         <v>1.22</v>
@@ -746,10 +746,10 @@
         <v>3.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
         <v>1.16</v>
@@ -761,28 +761,28 @@
         <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB2" t="n">
         <v>2.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5.87</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
         <v>3.35</v>
@@ -893,7 +893,7 @@
         <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
         <v>2</v>
@@ -905,7 +905,7 @@
         <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="V3" t="n">
         <v>1.34</v>
@@ -929,7 +929,7 @@
         <v>1.63</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.07</v>
+        <v>4.15</v>
       </c>
       <c r="AD3" t="n">
         <v>1.24</v>
@@ -1046,10 +1046,10 @@
         <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" t="n">
         <v>2.34</v>
@@ -1058,16 +1058,16 @@
         <v>2.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="U4" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
@@ -1082,25 +1082,25 @@
         <v>3.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
         <v>3.9</v>
@@ -1211,13 +1211,13 @@
         <v>4.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="R5" t="n">
         <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
@@ -1229,7 +1229,7 @@
         <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1247,16 +1247,16 @@
         <v>2.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD5" t="n">
         <v>1.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
         <v>2.5</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
         <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -1388,10 +1388,10 @@
         <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
         <v>1.34</v>
@@ -1406,7 +1406,7 @@
         <v>1.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AD6" t="n">
         <v>1.18</v>
@@ -1434,7 +1434,7 @@
         <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S3" t="n">
         <v>1.4</v>
@@ -905,13 +905,13 @@
         <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="V3" t="n">
         <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
@@ -926,13 +926,13 @@
         <v>2.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.15</v>
+        <v>3.84</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
         <v>1.06</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -725,43 +725,43 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.53</v>
@@ -770,16 +770,16 @@
         <v>2.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG2" t="n">
         <v>2.55</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>1.63</v>
       </c>
       <c r="O3" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.4</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
         <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.63</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.7</v>
-      </c>
       <c r="Q4" t="n">
-        <v>2.34</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>3.84</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
         <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.84</v>
+        <v>1.13</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,16 +1202,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
         <v>2.5</v>
@@ -1223,13 +1223,13 @@
         <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1238,25 +1238,25 @@
         <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA5" t="n">
         <v>1.49</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
         <v>1.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
         <v>2.5</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.63</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>3.84</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
         <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>1.13</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>1.63</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.63</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>2.34</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="S4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.4</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
         <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="O2" t="n">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="P2" t="n">
         <v>2.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R2" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="O3" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.4</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
         <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.63</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
         <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.7</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.34</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.88</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
         <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.84</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
         <v>3.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
         <v>2.5</v>
@@ -1220,7 +1220,7 @@
         <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
         <v>2.21</v>
@@ -1229,10 +1229,10 @@
         <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.12</v>
@@ -1256,10 +1256,10 @@
         <v>1.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S6" t="n">
         <v>1.44</v>
@@ -1403,7 +1403,7 @@
         <v>2.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
         <v>3.82</v>
@@ -1434,7 +1434,7 @@
         <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>5.95</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T3" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.44</v>
+        <v>2.74</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
         <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.85</v>
+        <v>1.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
         <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>3.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>2.48</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.75</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.9</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
         <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-08.xlsx
+++ b/jogos_2026-07-08.xlsx
@@ -702,57 +702,57 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
         <v>3.94</v>
       </c>
       <c r="P2" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="R2" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="S2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -761,71 +761,71 @@
         <v>1.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB2" t="n">
         <v>2.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AE2" t="n">
         <v>1.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '55', '66', '83']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46211.79166666666</v>
@@ -861,26 +861,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12', '90+4']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46211.83333333334</v>
@@ -1020,130 +1020,130 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
         <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69', '85']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '17']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46211.83333333334</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.94</v>
+        <v>4.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
         <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
         <v>2.25</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>3.15</v>
+        <v>3.03</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
         <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.02</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
